--- a/layout/Layout OFF_FX_V11_OFF_CONVAL.xlsx
+++ b/layout/Layout OFF_FX_V11_OFF_CONVAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963A9D2D-D7F6-4AF7-98B8-F74D52EC2777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360625CC-AB95-47E9-9FC2-E2CE502EE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12940" yWindow="5500" windowWidth="21830" windowHeight="13000" tabRatio="526" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12780" yWindow="5800" windowWidth="21830" windowHeight="13000" tabRatio="526" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFF CONVAL" sheetId="6" r:id="rId1"/>
@@ -902,6 +902,38 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -938,38 +970,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1082,13 +1082,13 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nombre" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo" dataDxfId="8"/>
     <tableColumn id="10" xr3:uid="{30F74211-651F-4A3E-A3BD-5A04ED448D42}" name="Formato" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{2BCB47CD-5255-4A80-8032-BA34EC72D88A}" name="Catalogo" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{BA34F110-C259-41E3-AD6B-64E1B2B28572}" name="Reportes Obligatorio" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{F3EF2AE6-E126-41AB-97B9-AB198FB749FA}" name="Validacion" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Uso" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Descripcion" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Reportes Opcional" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Comentario BW" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{2BCB47CD-5255-4A80-8032-BA34EC72D88A}" name="Catalogo" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{BA34F110-C259-41E3-AD6B-64E1B2B28572}" name="Reportes Obligatorio" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{F3EF2AE6-E126-41AB-97B9-AB198FB749FA}" name="Validacion" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Uso" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Descripcion" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Reportes Opcional" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Comentario BW" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1400,7 +1400,7 @@
     <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="97.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.453125" customWidth="1"/>
@@ -1928,6 +1928,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003EADB6AB950C774BBB9F1C75E500B284" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="101bf262c701ad3b79067f76f13f8957">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf35dce2-b600-471d-a6b0-9e8301b7851b" xmlns:ns3="3de82841-ffbb-418b-a888-39c303bacd30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a75b904d2a00e23a3c27f0f1b23bc34b" ns2:_="" ns3:_="">
     <xsd:import namespace="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
@@ -2128,15 +2137,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2149,6 +2149,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ACE9F6B-4C01-4F95-8EA7-48C4B89F8991}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{564CD401-B4EE-4DA6-809A-6F796899892E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2167,14 +2175,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ACE9F6B-4C01-4F95-8EA7-48C4B89F8991}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E002060D-AD3C-4874-B7EA-3C682E8960F4}">
   <ds:schemaRefs>

--- a/layout/Layout OFF_FX_V11_OFF_CONVAL.xlsx
+++ b/layout/Layout OFF_FX_V11_OFF_CONVAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360625CC-AB95-47E9-9FC2-E2CE502EE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A36786-64E4-4390-9DDC-54811CF52BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12780" yWindow="5800" windowWidth="21830" windowHeight="13000" tabRatio="526" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6972" yWindow="3936" windowWidth="17280" windowHeight="10500" tabRatio="526" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFF CONVAL" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="73">
   <si>
     <t>Descripcion</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>AAAA/MM/DD</t>
-  </si>
-  <si>
-    <t>Fecha a la que corresponde la información</t>
   </si>
   <si>
     <t>Validacion</t>
@@ -456,7 +453,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -642,8 +639,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -759,14 +768,43 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
         <color theme="8" tint="0.39997558519241921"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color theme="8" tint="0.39997558519241921"/>
-      </bottom>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -816,39 +854,82 @@
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -897,172 +978,7 @@
     <cellStyle name="Título 3" xfId="6" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <sz val="10"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="8" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1073,25 +989,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table245710527" displayName="Table245710527" ref="A1:K18" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11">
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Orden"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Nombre" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{30F74211-651F-4A3E-A3BD-5A04ED448D42}" name="Formato" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{2BCB47CD-5255-4A80-8032-BA34EC72D88A}" name="Catalogo" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{BA34F110-C259-41E3-AD6B-64E1B2B28572}" name="Reportes Obligatorio" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{F3EF2AE6-E126-41AB-97B9-AB198FB749FA}" name="Validacion" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Uso" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Descripcion" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Reportes Opcional" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Comentario BW" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1392,551 +1289,577 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="97.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.453125" customWidth="1"/>
-    <col min="11" max="11" width="38.36328125" customWidth="1"/>
-    <col min="12" max="12" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6328125" customWidth="1"/>
-    <col min="14" max="14" width="17.453125" customWidth="1"/>
-    <col min="15" max="15" width="19.6328125" customWidth="1"/>
+    <col min="9" max="9" width="97.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.44140625" customWidth="1"/>
+    <col min="11" max="11" width="38.33203125" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" customWidth="1"/>
+    <col min="15" max="15" width="19.6640625" customWidth="1"/>
     <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.36328125" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="B2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="14">
+        <v>20</v>
+      </c>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="20">
+        <v>1</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="14">
+        <v>2</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="20">
+        <v>2</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="14">
+        <v>20</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="B8" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="20">
+        <v>3</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
     </row>
-    <row r="2" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="9" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="14">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="20">
+        <v>3</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+    </row>
+    <row r="11" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="14">
+        <v>15</v>
+      </c>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="20">
+        <v>3</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+    </row>
+    <row r="13" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="14">
+        <v>5</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="20">
+        <v>5</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+    </row>
+    <row r="15" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="14">
+        <v>20</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="20">
+        <v>15</v>
+      </c>
+      <c r="E16" s="22"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+    </row>
+    <row r="17" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="14">
+        <v>3</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>17</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="E18" s="28"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
     </row>
-    <row r="3" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="5">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="5">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="5">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="5">
-        <v>3</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="5">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="5">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="5">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="5">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="5">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="5">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="5">
-        <v>20</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="5">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="G16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="5">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="G18" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="11"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
       <c r="K19" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003EADB6AB950C774BBB9F1C75E500B284" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="101bf262c701ad3b79067f76f13f8957">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf35dce2-b600-471d-a6b0-9e8301b7851b" xmlns:ns3="3de82841-ffbb-418b-a888-39c303bacd30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a75b904d2a00e23a3c27f0f1b23bc34b" ns2:_="" ns3:_="">
     <xsd:import namespace="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
@@ -2137,6 +2060,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2149,14 +2081,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ACE9F6B-4C01-4F95-8EA7-48C4B89F8991}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{564CD401-B4EE-4DA6-809A-6F796899892E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2175,6 +2099,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ACE9F6B-4C01-4F95-8EA7-48C4B89F8991}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E002060D-AD3C-4874-B7EA-3C682E8960F4}">
   <ds:schemaRefs>
